--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N42_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0003T0006Z000C1N42_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>47.67062010191296</v>
+        <v>7.746475766560856</v>
       </c>
       <c r="D2" t="n">
-        <v>37.16517186829626</v>
+        <v>6.039340428598143</v>
       </c>
       <c r="E2" t="n">
-        <v>11.43041341631529</v>
+        <v>1.857442180151235</v>
       </c>
       <c r="F2" t="n">
-        <v>19.8050001948346</v>
+        <v>3.218312531660622</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>59.84246419168929</v>
+        <v>9.72440043114951</v>
       </c>
       <c r="D3" t="n">
-        <v>59.51792581052955</v>
+        <v>9.671662944211052</v>
       </c>
       <c r="E3" t="n">
-        <v>11.43041341631529</v>
+        <v>1.857442180151235</v>
       </c>
       <c r="F3" t="n">
-        <v>19.8050001948346</v>
+        <v>3.218312531660622</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.67992368106932</v>
+        <v>6.285487598173765</v>
       </c>
       <c r="D4" t="n">
-        <v>5.303441317824771</v>
+        <v>0.8618092141465253</v>
       </c>
       <c r="E4" t="n">
-        <v>11.43041341631529</v>
+        <v>1.857442180151235</v>
       </c>
       <c r="F4" t="n">
-        <v>19.8050001948346</v>
+        <v>3.218312531660622</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>68.63089298593216</v>
+        <v>11.15252011021398</v>
       </c>
       <c r="D5" t="n">
-        <v>23.39508153332136</v>
+        <v>3.80170074916472</v>
       </c>
       <c r="E5" t="n">
-        <v>11.43041341631529</v>
+        <v>1.857442180151235</v>
       </c>
       <c r="F5" t="n">
-        <v>19.8050001948346</v>
+        <v>3.218312531660622</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
